--- a/Racecard_20260429.xlsx
+++ b/Racecard_20260429.xlsx
@@ -862,38 +862,38 @@
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>14.42</v>
+        <v>14.371</v>
       </c>
       <c r="AP2" t="n">
-        <v>23.121</v>
+        <v>23.042</v>
       </c>
       <c r="AQ2" t="n">
-        <v>23.917</v>
+        <v>23.836</v>
       </c>
       <c r="AR2" t="n">
-        <v>23.932</v>
+        <v>23.851</v>
       </c>
       <c r="AS2" t="n">
-        <v>23.978</v>
+        <v>23.896</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>37.541</v>
+        <v>37.413</v>
       </c>
       <c r="AW2" t="n">
-        <v>47.91</v>
+        <v>47.747</v>
       </c>
       <c r="AX2" t="n">
-        <v>47.91</v>
+        <v>47.747</v>
       </c>
       <c r="AY2" t="n">
-        <v>109.368</v>
+        <v>108.996</v>
       </c>
       <c r="AZ2" t="n">
-        <v>46.39</v>
+        <v>43.9</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1068,38 +1068,38 @@
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>14.662</v>
+        <v>14.613</v>
       </c>
       <c r="AP3" t="n">
-        <v>23.599</v>
+        <v>23.519</v>
       </c>
       <c r="AQ3" t="n">
-        <v>24.271</v>
+        <v>24.19</v>
       </c>
       <c r="AR3" t="n">
-        <v>24.041</v>
+        <v>23.96</v>
       </c>
       <c r="AS3" t="n">
-        <v>23.874</v>
+        <v>23.794</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>38.261</v>
+        <v>38.132</v>
       </c>
       <c r="AW3" t="n">
-        <v>47.915</v>
+        <v>47.754</v>
       </c>
       <c r="AX3" t="n">
-        <v>47.915</v>
+        <v>47.754</v>
       </c>
       <c r="AY3" t="n">
-        <v>110.447</v>
+        <v>110.076</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.29</v>
+        <v>16.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1274,38 +1274,38 @@
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>14.133</v>
+        <v>14.085</v>
       </c>
       <c r="AP4" t="n">
-        <v>24.059</v>
+        <v>23.977</v>
       </c>
       <c r="AQ4" t="n">
-        <v>24.491</v>
+        <v>24.409</v>
       </c>
       <c r="AR4" t="n">
-        <v>24.24</v>
+        <v>24.158</v>
       </c>
       <c r="AS4" t="n">
-        <v>23.867</v>
+        <v>23.787</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
         <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>38.192</v>
+        <v>38.062</v>
       </c>
       <c r="AW4" t="n">
-        <v>48.107</v>
+        <v>47.945</v>
       </c>
       <c r="AX4" t="n">
-        <v>48.107</v>
+        <v>47.945</v>
       </c>
       <c r="AY4" t="n">
-        <v>110.79</v>
+        <v>110.416</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.63</v>
+        <v>11.94</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -1480,38 +1480,38 @@
       </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>14.387</v>
+        <v>14.338</v>
       </c>
       <c r="AP5" t="n">
-        <v>23.147</v>
+        <v>23.068</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24.604</v>
+        <v>24.52</v>
       </c>
       <c r="AR5" t="n">
-        <v>24.732</v>
+        <v>24.648</v>
       </c>
       <c r="AS5" t="n">
-        <v>24.011</v>
+        <v>23.929</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
         <v>3</v>
       </c>
       <c r="AV5" t="n">
-        <v>37.534</v>
+        <v>37.406</v>
       </c>
       <c r="AW5" t="n">
-        <v>48.743</v>
+        <v>48.577</v>
       </c>
       <c r="AX5" t="n">
-        <v>48.743</v>
+        <v>48.577</v>
       </c>
       <c r="AY5" t="n">
-        <v>110.881</v>
+        <v>110.503</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.62</v>
+        <v>11.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -1686,38 +1686,38 @@
       </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>13.949</v>
+        <v>13.901</v>
       </c>
       <c r="AP6" t="n">
-        <v>23.236</v>
+        <v>23.157</v>
       </c>
       <c r="AQ6" t="n">
-        <v>24.595</v>
+        <v>24.512</v>
       </c>
       <c r="AR6" t="n">
-        <v>24.911</v>
+        <v>24.827</v>
       </c>
       <c r="AS6" t="n">
-        <v>24.359</v>
+        <v>24.276</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
         <v>2</v>
       </c>
       <c r="AV6" t="n">
-        <v>37.185</v>
+        <v>37.058</v>
       </c>
       <c r="AW6" t="n">
-        <v>49.27</v>
+        <v>49.103</v>
       </c>
       <c r="AX6" t="n">
-        <v>49.27</v>
+        <v>49.103</v>
       </c>
       <c r="AY6" t="n">
-        <v>111.05</v>
+        <v>110.673</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9.960000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -1888,38 +1888,38 @@
       </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>13.912</v>
+        <v>13.865</v>
       </c>
       <c r="AP7" t="n">
-        <v>23.822</v>
+        <v>23.742</v>
       </c>
       <c r="AQ7" t="n">
-        <v>24.483</v>
+        <v>24.401</v>
       </c>
       <c r="AR7" t="n">
-        <v>24.777</v>
+        <v>24.694</v>
       </c>
       <c r="AS7" t="n">
-        <v>25.747</v>
+        <v>25.66</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="n">
         <v>2</v>
       </c>
       <c r="AV7" t="n">
-        <v>37.734</v>
+        <v>37.607</v>
       </c>
       <c r="AW7" t="n">
-        <v>50.524</v>
+        <v>50.354</v>
       </c>
       <c r="AX7" t="n">
-        <v>50.524</v>
+        <v>50.354</v>
       </c>
       <c r="AY7" t="n">
-        <v>112.741</v>
+        <v>112.362</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -2090,7 +2090,9 @@
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
+      <c r="AZ8" t="n">
+        <v>0.9</v>
+      </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
@@ -2248,7 +2250,9 @@
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>0.9</v>
+      </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
@@ -2406,7 +2410,9 @@
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>0.9</v>
+      </c>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr"/>
@@ -2564,7 +2570,9 @@
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>0.9</v>
+      </c>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -2722,7 +2730,9 @@
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>0.9</v>
+      </c>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -2880,7 +2890,9 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>0.9</v>
+      </c>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -3340,13 +3352,13 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>23.513</v>
+        <v>23.433</v>
       </c>
       <c r="AP2" t="n">
-        <v>22.848</v>
+        <v>22.77</v>
       </c>
       <c r="AQ2" t="n">
-        <v>23.651</v>
+        <v>23.571</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
@@ -3355,19 +3367,19 @@
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>46.361</v>
+        <v>46.203</v>
       </c>
       <c r="AW2" t="n">
-        <v>46.499</v>
+        <v>46.341</v>
       </c>
       <c r="AX2" t="n">
-        <v>46.499</v>
+        <v>46.341</v>
       </c>
       <c r="AY2" t="n">
-        <v>70.012</v>
+        <v>69.774</v>
       </c>
       <c r="AZ2" t="n">
-        <v>34.72</v>
+        <v>34.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -3544,13 +3556,13 @@
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>24.132</v>
+        <v>24.051</v>
       </c>
       <c r="AP3" t="n">
-        <v>22.8</v>
+        <v>22.724</v>
       </c>
       <c r="AQ3" t="n">
-        <v>23.324</v>
+        <v>23.245</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
@@ -3559,19 +3571,19 @@
         <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>46.932</v>
+        <v>46.775</v>
       </c>
       <c r="AW3" t="n">
-        <v>46.124</v>
+        <v>45.969</v>
       </c>
       <c r="AX3" t="n">
-        <v>46.124</v>
+        <v>45.969</v>
       </c>
       <c r="AY3" t="n">
-        <v>70.256</v>
+        <v>70.02</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22.29</v>
+        <v>21.77</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -3748,13 +3760,13 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>24.399</v>
+        <v>24.316</v>
       </c>
       <c r="AP4" t="n">
-        <v>22.917</v>
+        <v>22.839</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23.241</v>
+        <v>23.162</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
@@ -3763,19 +3775,19 @@
         <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>47.316</v>
+        <v>47.155</v>
       </c>
       <c r="AW4" t="n">
-        <v>46.158</v>
+        <v>46.001</v>
       </c>
       <c r="AX4" t="n">
-        <v>46.158</v>
+        <v>46.001</v>
       </c>
       <c r="AY4" t="n">
-        <v>70.557</v>
+        <v>70.31699999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.9</v>
+        <v>12.68</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -3952,13 +3964,13 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>23.924</v>
+        <v>23.843</v>
       </c>
       <c r="AP5" t="n">
-        <v>22.996</v>
+        <v>22.918</v>
       </c>
       <c r="AQ5" t="n">
-        <v>23.746</v>
+        <v>23.666</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
@@ -3967,19 +3979,19 @@
         <v>3</v>
       </c>
       <c r="AV5" t="n">
-        <v>46.92</v>
+        <v>46.761</v>
       </c>
       <c r="AW5" t="n">
-        <v>46.742</v>
+        <v>46.584</v>
       </c>
       <c r="AX5" t="n">
-        <v>46.742</v>
+        <v>46.584</v>
       </c>
       <c r="AY5" t="n">
-        <v>70.666</v>
+        <v>70.42700000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10.59</v>
+        <v>10.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -4156,13 +4168,13 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>24.928</v>
+        <v>24.844</v>
       </c>
       <c r="AP6" t="n">
-        <v>22.892</v>
+        <v>22.814</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23.168</v>
+        <v>23.089</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
@@ -4171,19 +4183,19 @@
         <v>3</v>
       </c>
       <c r="AV6" t="n">
-        <v>47.82</v>
+        <v>47.658</v>
       </c>
       <c r="AW6" t="n">
-        <v>46.06</v>
+        <v>45.903</v>
       </c>
       <c r="AX6" t="n">
-        <v>46.06</v>
+        <v>45.903</v>
       </c>
       <c r="AY6" t="n">
-        <v>70.988</v>
+        <v>70.747</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.9</v>
+        <v>5.79</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -4360,13 +4372,13 @@
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>23.917</v>
+        <v>23.836</v>
       </c>
       <c r="AP7" t="n">
-        <v>22.949</v>
+        <v>22.872</v>
       </c>
       <c r="AQ7" t="n">
-        <v>24.215</v>
+        <v>24.133</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
@@ -4375,19 +4387,19 @@
         <v>3</v>
       </c>
       <c r="AV7" t="n">
-        <v>46.866</v>
+        <v>46.708</v>
       </c>
       <c r="AW7" t="n">
-        <v>47.164</v>
+        <v>47.005</v>
       </c>
       <c r="AX7" t="n">
-        <v>47.164</v>
+        <v>47.005</v>
       </c>
       <c r="AY7" t="n">
-        <v>71.081</v>
+        <v>70.84099999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.98</v>
+        <v>4.88</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -4564,13 +4576,13 @@
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>24.322</v>
+        <v>24.24</v>
       </c>
       <c r="AP8" t="n">
-        <v>23.058</v>
+        <v>22.981</v>
       </c>
       <c r="AQ8" t="n">
-        <v>23.79</v>
+        <v>23.709</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
@@ -4579,19 +4591,19 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>47.38</v>
+        <v>47.221</v>
       </c>
       <c r="AW8" t="n">
-        <v>46.848</v>
+        <v>46.69</v>
       </c>
       <c r="AX8" t="n">
-        <v>46.848</v>
+        <v>46.69</v>
       </c>
       <c r="AY8" t="n">
-        <v>71.17</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.24</v>
+        <v>4.15</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -4768,13 +4780,13 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>24.744</v>
+        <v>24.661</v>
       </c>
       <c r="AP9" t="n">
-        <v>22.906</v>
+        <v>22.829</v>
       </c>
       <c r="AQ9" t="n">
-        <v>23.733</v>
+        <v>23.653</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
@@ -4783,19 +4795,19 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>47.65</v>
+        <v>47.49</v>
       </c>
       <c r="AW9" t="n">
-        <v>46.639</v>
+        <v>46.482</v>
       </c>
       <c r="AX9" t="n">
-        <v>46.639</v>
+        <v>46.482</v>
       </c>
       <c r="AY9" t="n">
-        <v>71.383</v>
+        <v>71.143</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4972,13 +4984,13 @@
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
-        <v>24.778</v>
+        <v>24.694</v>
       </c>
       <c r="AP10" t="n">
-        <v>22.99</v>
+        <v>22.912</v>
       </c>
       <c r="AQ10" t="n">
-        <v>23.975</v>
+        <v>23.894</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
@@ -4987,19 +4999,19 @@
         <v>3</v>
       </c>
       <c r="AV10" t="n">
-        <v>47.768</v>
+        <v>47.606</v>
       </c>
       <c r="AW10" t="n">
-        <v>46.965</v>
+        <v>46.806</v>
       </c>
       <c r="AX10" t="n">
-        <v>46.965</v>
+        <v>46.806</v>
       </c>
       <c r="AY10" t="n">
-        <v>71.74299999999999</v>
+        <v>71.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -5172,7 +5184,9 @@
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>0.66</v>
+      </c>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -5332,7 +5346,9 @@
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>0.66</v>
+      </c>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -5400,7 +5416,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>潘明輝</t>
+          <t>楊明綸</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -5496,11 +5512,17 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>0.66</v>
+      </c>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>21%(3/14)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5952,40 +5974,40 @@
         <v>24.06</v>
       </c>
       <c r="AO2" t="n">
-        <v>15.129</v>
+        <v>15.078</v>
       </c>
       <c r="AP2" t="n">
-        <v>24.027</v>
+        <v>23.946</v>
       </c>
       <c r="AQ2" t="n">
-        <v>24.68</v>
+        <v>24.597</v>
       </c>
       <c r="AR2" t="n">
-        <v>24.281</v>
+        <v>24.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>24.302</v>
+        <v>24.22</v>
       </c>
       <c r="AT2" t="n">
-        <v>24.292</v>
+        <v>24.21</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>39.156</v>
+        <v>39.024</v>
       </c>
       <c r="AW2" t="n">
-        <v>48.594</v>
+        <v>48.43</v>
       </c>
       <c r="AX2" t="n">
-        <v>48.594</v>
+        <v>48.43</v>
       </c>
       <c r="AY2" t="n">
-        <v>136.711</v>
+        <v>136.251</v>
       </c>
       <c r="AZ2" t="n">
-        <v>23.27</v>
+        <v>22.63</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -6162,40 +6184,40 @@
         <v>24.13</v>
       </c>
       <c r="AO3" t="n">
-        <v>15.1</v>
+        <v>15.048</v>
       </c>
       <c r="AP3" t="n">
-        <v>24.149</v>
+        <v>24.067</v>
       </c>
       <c r="AQ3" t="n">
-        <v>24.911</v>
+        <v>24.826</v>
       </c>
       <c r="AR3" t="n">
-        <v>24.35</v>
+        <v>24.267</v>
       </c>
       <c r="AS3" t="n">
-        <v>24.12</v>
+        <v>24.038</v>
       </c>
       <c r="AT3" t="n">
-        <v>24.11</v>
+        <v>24.028</v>
       </c>
       <c r="AU3" t="n">
         <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>39.249</v>
+        <v>39.115</v>
       </c>
       <c r="AW3" t="n">
-        <v>48.23</v>
+        <v>48.066</v>
       </c>
       <c r="AX3" t="n">
-        <v>48.23</v>
+        <v>48.066</v>
       </c>
       <c r="AY3" t="n">
-        <v>136.74</v>
+        <v>136.274</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22.52</v>
+        <v>22.06</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -6372,40 +6394,40 @@
         <v>24.751</v>
       </c>
       <c r="AO4" t="n">
-        <v>15.125</v>
+        <v>15.074</v>
       </c>
       <c r="AP4" t="n">
-        <v>23.902</v>
+        <v>23.821</v>
       </c>
       <c r="AQ4" t="n">
-        <v>24.518</v>
+        <v>24.435</v>
       </c>
       <c r="AR4" t="n">
-        <v>24.237</v>
+        <v>24.154</v>
       </c>
       <c r="AS4" t="n">
-        <v>24.603</v>
+        <v>24.519</v>
       </c>
       <c r="AT4" t="n">
-        <v>24.862</v>
+        <v>24.777</v>
       </c>
       <c r="AU4" t="n">
         <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>39.027</v>
+        <v>38.895</v>
       </c>
       <c r="AW4" t="n">
-        <v>49.465</v>
+        <v>49.296</v>
       </c>
       <c r="AX4" t="n">
-        <v>49.465</v>
+        <v>49.296</v>
       </c>
       <c r="AY4" t="n">
-        <v>137.247</v>
+        <v>136.78</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.73</v>
+        <v>12.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -6459,65 +6481,65 @@
         <v>2200</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3/2/2/2/2/8</t>
+          <t>4/9/5/6/9/10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>夢照發</t>
+          <t>清雲龍駒</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H168</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K160</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>H168</t>
+          <t>K160</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>巴度</t>
+          <t>奧爾民</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>黎昭昇</t>
+          <t>賀賢</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="U5" t="n">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="V5" t="n">
-        <v>-19</v>
+        <v>-4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.15.75</t>
+          <t>2.15.47</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
@@ -6527,95 +6549,99 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>963,000</t>
+          <t>182,950</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>+ 1</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>天寶團體</t>
+          <t>洪祖杭與洪羽緁</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>Fascinating Rock</t>
+          <t>Galileo</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Ataahua</t>
+          <t>Different League</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>14.63</v>
+        <v>14.498</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23.877</v>
+        <v>23.51</v>
       </c>
       <c r="AK5" t="n">
-        <v>24.707</v>
+        <v>24.684</v>
       </c>
       <c r="AL5" t="n">
-        <v>24.647</v>
+        <v>24.613</v>
       </c>
       <c r="AM5" t="n">
-        <v>24.593</v>
+        <v>24.383</v>
       </c>
       <c r="AN5" t="n">
-        <v>24.683</v>
+        <v>24.313</v>
       </c>
       <c r="AO5" t="n">
-        <v>14.955</v>
+        <v>14.815</v>
       </c>
       <c r="AP5" t="n">
-        <v>24.038</v>
+        <v>23.692</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24.727</v>
+        <v>24.756</v>
       </c>
       <c r="AR5" t="n">
-        <v>24.59</v>
+        <v>24.738</v>
       </c>
       <c r="AS5" t="n">
-        <v>24.535</v>
+        <v>24.507</v>
       </c>
       <c r="AT5" t="n">
-        <v>24.626</v>
+        <v>24.437</v>
       </c>
       <c r="AU5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV5" t="n">
-        <v>38.993</v>
+        <v>38.507</v>
       </c>
       <c r="AW5" t="n">
-        <v>49.161</v>
+        <v>48.944</v>
       </c>
       <c r="AX5" t="n">
-        <v>49.161</v>
+        <v>48.944</v>
       </c>
       <c r="AY5" t="n">
-        <v>137.471</v>
+        <v>136.945</v>
       </c>
       <c r="AZ5" t="n">
-        <v>9.9</v>
+        <v>10.37</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3-2-3-3-4-4</t>
+          <t>1-1-1-3-5-4</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -6625,12 +6651,12 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>外疊搶放 (外檔, 頭段排名2)</t>
+          <t>外疊搶放 (外檔, 頭段排名1)</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>35%(7/20)</t>
+          <t>26%(8/31)</t>
         </is>
       </c>
     </row>
@@ -6665,65 +6691,65 @@
         <v>2200</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4/9/5/6/9/10</t>
+          <t>3/2/2/2/2/8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>清雲龍駒</t>
+          <t>夢照發</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K160</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H168</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>K160</t>
+          <t>H168</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>潘明輝</t>
+          <t>巴度</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>賀賢</t>
+          <t>黎昭昇</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="T6" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="V6" t="n">
-        <v>-4</v>
+        <v>-19</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.15.47</t>
+          <t>2.15.75</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
@@ -6733,99 +6759,95 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>182,950</t>
+          <t>963,000</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>+ 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>31</v>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>洪祖杭與洪羽緁</t>
+          <t>天寶團體</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>Galileo</t>
+          <t>Fascinating Rock</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Different League</t>
+          <t>Ataahua</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>14.498</v>
+        <v>14.63</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23.51</v>
+        <v>23.877</v>
       </c>
       <c r="AK6" t="n">
-        <v>24.684</v>
+        <v>24.707</v>
       </c>
       <c r="AL6" t="n">
-        <v>24.613</v>
+        <v>24.647</v>
       </c>
       <c r="AM6" t="n">
-        <v>24.383</v>
+        <v>24.593</v>
       </c>
       <c r="AN6" t="n">
-        <v>24.313</v>
+        <v>24.683</v>
       </c>
       <c r="AO6" t="n">
-        <v>14.877</v>
+        <v>14.904</v>
       </c>
       <c r="AP6" t="n">
-        <v>23.791</v>
+        <v>23.956</v>
       </c>
       <c r="AQ6" t="n">
-        <v>24.859</v>
+        <v>24.643</v>
       </c>
       <c r="AR6" t="n">
-        <v>24.841</v>
+        <v>24.506</v>
       </c>
       <c r="AS6" t="n">
-        <v>24.61</v>
+        <v>24.452</v>
       </c>
       <c r="AT6" t="n">
-        <v>24.539</v>
+        <v>24.542</v>
       </c>
       <c r="AU6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV6" t="n">
-        <v>38.668</v>
+        <v>38.86</v>
       </c>
       <c r="AW6" t="n">
-        <v>49.149</v>
+        <v>48.994</v>
       </c>
       <c r="AX6" t="n">
-        <v>49.149</v>
+        <v>48.994</v>
       </c>
       <c r="AY6" t="n">
-        <v>137.517</v>
+        <v>137.003</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9.4</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1-1-1-4-5-5</t>
+          <t>3-2-3-4-4-5</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -6835,12 +6857,12 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>外疊搶放 (外檔, 頭段排名1)</t>
+          <t>外疊搶放 (外檔, 頭段排名2)</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>22%(7/32)</t>
+          <t>35%(7/20)</t>
         </is>
       </c>
     </row>
@@ -6998,40 +7020,40 @@
         <v>24.099</v>
       </c>
       <c r="AO7" t="n">
-        <v>15.301</v>
+        <v>15.25</v>
       </c>
       <c r="AP7" t="n">
-        <v>23.991</v>
+        <v>23.91</v>
       </c>
       <c r="AQ7" t="n">
-        <v>24.979</v>
+        <v>24.895</v>
       </c>
       <c r="AR7" t="n">
-        <v>24.719</v>
+        <v>24.636</v>
       </c>
       <c r="AS7" t="n">
-        <v>24.449</v>
+        <v>24.366</v>
       </c>
       <c r="AT7" t="n">
-        <v>24.15</v>
+        <v>24.068</v>
       </c>
       <c r="AU7" t="n">
         <v>3</v>
       </c>
       <c r="AV7" t="n">
-        <v>39.292</v>
+        <v>39.16</v>
       </c>
       <c r="AW7" t="n">
-        <v>48.599</v>
+        <v>48.434</v>
       </c>
       <c r="AX7" t="n">
-        <v>48.599</v>
+        <v>48.434</v>
       </c>
       <c r="AY7" t="n">
-        <v>137.589</v>
+        <v>137.125</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8.67</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -7208,40 +7230,40 @@
         <v>24.58</v>
       </c>
       <c r="AO8" t="n">
-        <v>14.946</v>
+        <v>14.895</v>
       </c>
       <c r="AP8" t="n">
-        <v>24.777</v>
+        <v>24.693</v>
       </c>
       <c r="AQ8" t="n">
-        <v>24.373</v>
+        <v>24.291</v>
       </c>
       <c r="AR8" t="n">
-        <v>24.653</v>
+        <v>24.57</v>
       </c>
       <c r="AS8" t="n">
-        <v>24.443</v>
+        <v>24.36</v>
       </c>
       <c r="AT8" t="n">
-        <v>24.633</v>
+        <v>24.55</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>39.723</v>
+        <v>39.588</v>
       </c>
       <c r="AW8" t="n">
-        <v>49.076</v>
+        <v>48.91</v>
       </c>
       <c r="AX8" t="n">
-        <v>49.076</v>
+        <v>48.91</v>
       </c>
       <c r="AY8" t="n">
-        <v>137.825</v>
+        <v>137.359</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.65</v>
+        <v>6.51</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -7418,40 +7440,40 @@
         <v>24.235</v>
       </c>
       <c r="AO9" t="n">
-        <v>14.983</v>
+        <v>14.932</v>
       </c>
       <c r="AP9" t="n">
-        <v>24.369</v>
+        <v>24.287</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24.652</v>
+        <v>24.569</v>
       </c>
       <c r="AR9" t="n">
-        <v>24.655</v>
+        <v>24.572</v>
       </c>
       <c r="AS9" t="n">
-        <v>24.781</v>
+        <v>24.697</v>
       </c>
       <c r="AT9" t="n">
-        <v>24.463</v>
+        <v>24.381</v>
       </c>
       <c r="AU9" t="n">
         <v>2</v>
       </c>
       <c r="AV9" t="n">
-        <v>39.352</v>
+        <v>39.219</v>
       </c>
       <c r="AW9" t="n">
-        <v>49.244</v>
+        <v>49.078</v>
       </c>
       <c r="AX9" t="n">
-        <v>49.244</v>
+        <v>49.078</v>
       </c>
       <c r="AY9" t="n">
-        <v>137.903</v>
+        <v>137.438</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.09</v>
+        <v>5.95</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -7628,40 +7650,40 @@
         <v>24.75</v>
       </c>
       <c r="AO10" t="n">
-        <v>15.142</v>
+        <v>15.091</v>
       </c>
       <c r="AP10" t="n">
-        <v>24.771</v>
+        <v>24.687</v>
       </c>
       <c r="AQ10" t="n">
-        <v>25.546</v>
+        <v>25.46</v>
       </c>
       <c r="AR10" t="n">
-        <v>25.564</v>
+        <v>25.478</v>
       </c>
       <c r="AS10" t="n">
-        <v>23.812</v>
+        <v>23.731</v>
       </c>
       <c r="AT10" t="n">
-        <v>24.89</v>
+        <v>24.805</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>39.913</v>
+        <v>39.778</v>
       </c>
       <c r="AW10" t="n">
-        <v>48.702</v>
+        <v>48.536</v>
       </c>
       <c r="AX10" t="n">
-        <v>48.702</v>
+        <v>48.536</v>
       </c>
       <c r="AY10" t="n">
-        <v>139.725</v>
+        <v>139.252</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -7832,7 +7854,9 @@
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>0.35</v>
+      </c>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -7990,7 +8014,9 @@
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>0.35</v>
+      </c>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -8148,7 +8174,9 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>0.35</v>
+      </c>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -8602,13 +8630,13 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>24.053</v>
+        <v>23.984</v>
       </c>
       <c r="AP2" t="n">
-        <v>22.408</v>
+        <v>22.343</v>
       </c>
       <c r="AQ2" t="n">
-        <v>22.826</v>
+        <v>22.76</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
@@ -8617,19 +8645,19 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>46.461</v>
+        <v>46.327</v>
       </c>
       <c r="AW2" t="n">
-        <v>45.234</v>
+        <v>45.103</v>
       </c>
       <c r="AX2" t="n">
-        <v>45.234</v>
+        <v>45.103</v>
       </c>
       <c r="AY2" t="n">
-        <v>69.28700000000001</v>
+        <v>69.087</v>
       </c>
       <c r="AZ2" t="n">
-        <v>40.13</v>
+        <v>40.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -8802,13 +8830,13 @@
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>24.581</v>
+        <v>24.497</v>
       </c>
       <c r="AP3" t="n">
-        <v>22.1</v>
+        <v>22.025</v>
       </c>
       <c r="AQ3" t="n">
-        <v>23.149</v>
+        <v>23.07</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
@@ -8817,19 +8845,19 @@
         <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>46.681</v>
+        <v>46.522</v>
       </c>
       <c r="AW3" t="n">
-        <v>45.249</v>
+        <v>45.095</v>
       </c>
       <c r="AX3" t="n">
-        <v>45.249</v>
+        <v>45.095</v>
       </c>
       <c r="AY3" t="n">
-        <v>69.83</v>
+        <v>69.592</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16.88</v>
+        <v>17.89</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -9002,13 +9030,13 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>24.377</v>
+        <v>24.294</v>
       </c>
       <c r="AP4" t="n">
-        <v>22.681</v>
+        <v>22.604</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23.101</v>
+        <v>23.023</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
@@ -9017,23 +9045,23 @@
         <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>47.058</v>
+        <v>46.898</v>
       </c>
       <c r="AW4" t="n">
-        <v>45.782</v>
+        <v>45.627</v>
       </c>
       <c r="AX4" t="n">
-        <v>45.782</v>
+        <v>45.627</v>
       </c>
       <c r="AY4" t="n">
-        <v>70.15900000000001</v>
+        <v>69.92100000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9.98</v>
+        <v>10.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5-6-3</t>
+          <t>4-5-3</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -9043,7 +9071,7 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>中置守位 (中檔, 頭段排名6)</t>
+          <t>中置守位 (中檔, 頭段排名5)</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
@@ -9200,13 +9228,13 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>23.945</v>
+        <v>23.864</v>
       </c>
       <c r="AP5" t="n">
-        <v>22.497</v>
+        <v>22.421</v>
       </c>
       <c r="AQ5" t="n">
-        <v>23.862</v>
+        <v>23.782</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
@@ -9215,19 +9243,19 @@
         <v>3</v>
       </c>
       <c r="AV5" t="n">
-        <v>46.442</v>
+        <v>46.285</v>
       </c>
       <c r="AW5" t="n">
-        <v>46.359</v>
+        <v>46.203</v>
       </c>
       <c r="AX5" t="n">
-        <v>46.359</v>
+        <v>46.203</v>
       </c>
       <c r="AY5" t="n">
-        <v>70.304</v>
+        <v>70.06699999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.92</v>
+        <v>8.27</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -9281,65 +9309,65 @@
         <v>1200</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12/9</t>
+          <t>6/8/4/6/7/5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>悠然常勝</t>
+          <t>紅愛舍</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2025_L136</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H110</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>L136</t>
+          <t>H110</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>布浩榮</t>
+          <t>布文</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>巫偉傑</t>
+          <t>韋達</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="T6" t="n">
         <v>-2</v>
       </c>
       <c r="U6" t="n">
-        <v>1018</v>
+        <v>1166</v>
       </c>
       <c r="V6" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.10.39</t>
+          <t>1.09.26</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
@@ -9349,102 +9377,102 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>441,600</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>* 2</t>
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>H/P/TT</t>
+          <t>B/TT</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>優悠團體</t>
+          <t>李卓然先生及夫人</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>Ace High</t>
+          <t>Frankel</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Smokin' Valentina</t>
+          <t>Spring In The Air</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>24.375</v>
+        <v>24.384</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22.726</v>
+        <v>22.552</v>
       </c>
       <c r="AK6" t="n">
-        <v>23.711</v>
+        <v>23.166</v>
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>24.326</v>
+        <v>24.381</v>
       </c>
       <c r="AP6" t="n">
-        <v>22.55</v>
+        <v>22.625</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23.437</v>
+        <v>23.285</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV6" t="n">
-        <v>46.876</v>
+        <v>47.006</v>
       </c>
       <c r="AW6" t="n">
-        <v>45.987</v>
+        <v>45.91</v>
       </c>
       <c r="AX6" t="n">
-        <v>45.987</v>
+        <v>45.91</v>
       </c>
       <c r="AY6" t="n">
-        <v>70.313</v>
+        <v>70.291</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7.81</v>
+        <v>5.75</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4-5-5</t>
+          <t>5-7-5</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>中置守位</t>
+          <t>包廂跟前</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>中置守位 (外檔, 頭段排名5)</t>
+          <t>包廂跟前 (內檔, 頭段排名7)</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>100%(2/2)</t>
+          <t>15%(2/13)</t>
         </is>
       </c>
     </row>
@@ -9479,65 +9507,65 @@
         <v>1200</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6/8/4/6/7/5</t>
+          <t>12/9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>紅愛舍</t>
+          <t>悠然常勝</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H110</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2025_L136</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>H110</t>
+          <t>L136</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>布文</t>
+          <t>布浩榮</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>韋達</t>
+          <t>巫偉傑</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="T7" t="n">
         <v>-2</v>
       </c>
       <c r="U7" t="n">
-        <v>1166</v>
+        <v>1018</v>
       </c>
       <c r="V7" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.09.26</t>
+          <t>1.10.39</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
@@ -9547,102 +9575,102 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>441,600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>* 2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>B/TT</t>
+          <t>H/P/TT</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>李卓然先生及夫人</t>
+          <t>優悠團體</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>Frankel</t>
+          <t>Ace High</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Spring In The Air</t>
+          <t>Smokin' Valentina</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>24.384</v>
+        <v>24.375</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22.552</v>
+        <v>22.726</v>
       </c>
       <c r="AK7" t="n">
-        <v>23.166</v>
+        <v>23.711</v>
       </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>24.463</v>
+        <v>24.39</v>
       </c>
       <c r="AP7" t="n">
-        <v>22.702</v>
+        <v>22.609</v>
       </c>
       <c r="AQ7" t="n">
-        <v>23.364</v>
+        <v>23.499</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>47.165</v>
+        <v>46.999</v>
       </c>
       <c r="AW7" t="n">
-        <v>46.066</v>
+        <v>46.108</v>
       </c>
       <c r="AX7" t="n">
-        <v>46.066</v>
+        <v>46.108</v>
       </c>
       <c r="AY7" t="n">
-        <v>70.529</v>
+        <v>70.498</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.53</v>
+        <v>4.11</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6-7-6</t>
+          <t>6-6-6</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>包廂跟前</t>
+          <t>中置守位</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>包廂跟前 (內檔, 頭段排名7)</t>
+          <t>中置守位 (外檔, 頭段排名6)</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>15%(2/13)</t>
+          <t>100%(2/2)</t>
         </is>
       </c>
     </row>
@@ -9794,13 +9822,13 @@
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>24.747</v>
+        <v>24.664</v>
       </c>
       <c r="AP8" t="n">
-        <v>23.054</v>
+        <v>22.976</v>
       </c>
       <c r="AQ8" t="n">
-        <v>23.016</v>
+        <v>22.938</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
@@ -9809,19 +9837,19 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>47.801</v>
+        <v>47.64</v>
       </c>
       <c r="AW8" t="n">
-        <v>46.07</v>
+        <v>45.914</v>
       </c>
       <c r="AX8" t="n">
-        <v>46.07</v>
+        <v>45.914</v>
       </c>
       <c r="AY8" t="n">
-        <v>70.81699999999999</v>
+        <v>70.578</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.49</v>
+        <v>3.61</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -9988,13 +10016,13 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>23.768</v>
+        <v>23.688</v>
       </c>
       <c r="AP9" t="n">
-        <v>22.817</v>
+        <v>22.739</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24.482</v>
+        <v>24.399</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
@@ -10003,19 +10031,19 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>46.585</v>
+        <v>46.427</v>
       </c>
       <c r="AW9" t="n">
-        <v>47.299</v>
+        <v>47.138</v>
       </c>
       <c r="AX9" t="n">
-        <v>47.299</v>
+        <v>47.138</v>
       </c>
       <c r="AY9" t="n">
-        <v>71.06699999999999</v>
+        <v>70.82599999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -10186,13 +10214,13 @@
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
-        <v>24.512</v>
+        <v>24.429</v>
       </c>
       <c r="AP10" t="n">
-        <v>22.948</v>
+        <v>22.87</v>
       </c>
       <c r="AQ10" t="n">
-        <v>23.618</v>
+        <v>23.538</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
@@ -10201,19 +10229,19 @@
         <v>2</v>
       </c>
       <c r="AV10" t="n">
-        <v>47.46</v>
+        <v>47.299</v>
       </c>
       <c r="AW10" t="n">
-        <v>46.566</v>
+        <v>46.408</v>
       </c>
       <c r="AX10" t="n">
-        <v>46.566</v>
+        <v>46.408</v>
       </c>
       <c r="AY10" t="n">
-        <v>71.078</v>
+        <v>70.837</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -10384,13 +10412,13 @@
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
-        <v>24.577</v>
+        <v>24.494</v>
       </c>
       <c r="AP11" t="n">
-        <v>23.085</v>
+        <v>23.007</v>
       </c>
       <c r="AQ11" t="n">
-        <v>23.562</v>
+        <v>23.482</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr"/>
@@ -10399,19 +10427,19 @@
         <v>3</v>
       </c>
       <c r="AV11" t="n">
-        <v>47.662</v>
+        <v>47.501</v>
       </c>
       <c r="AW11" t="n">
-        <v>46.647</v>
+        <v>46.489</v>
       </c>
       <c r="AX11" t="n">
-        <v>46.647</v>
+        <v>46.489</v>
       </c>
       <c r="AY11" t="n">
-        <v>71.224</v>
+        <v>70.983</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -10582,13 +10610,13 @@
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
-        <v>24.692</v>
+        <v>24.608</v>
       </c>
       <c r="AP12" t="n">
-        <v>22.834</v>
+        <v>22.757</v>
       </c>
       <c r="AQ12" t="n">
-        <v>23.715</v>
+        <v>23.635</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="inlineStr"/>
@@ -10597,19 +10625,19 @@
         <v>3</v>
       </c>
       <c r="AV12" t="n">
-        <v>47.526</v>
+        <v>47.365</v>
       </c>
       <c r="AW12" t="n">
-        <v>46.549</v>
+        <v>46.392</v>
       </c>
       <c r="AX12" t="n">
-        <v>46.549</v>
+        <v>46.392</v>
       </c>
       <c r="AY12" t="n">
-        <v>71.241</v>
+        <v>71</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -10776,7 +10804,9 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>0.82</v>
+      </c>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -11230,13 +11260,13 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>24.271</v>
+        <v>24.188</v>
       </c>
       <c r="AP2" t="n">
-        <v>22.631</v>
+        <v>22.555</v>
       </c>
       <c r="AQ2" t="n">
-        <v>23.527</v>
+        <v>23.447</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
@@ -11245,19 +11275,19 @@
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>46.902</v>
+        <v>46.743</v>
       </c>
       <c r="AW2" t="n">
-        <v>46.158</v>
+        <v>46.002</v>
       </c>
       <c r="AX2" t="n">
-        <v>46.158</v>
+        <v>46.002</v>
       </c>
       <c r="AY2" t="n">
-        <v>70.429</v>
+        <v>70.19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>23.53</v>
+        <v>23.07</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -11428,13 +11458,13 @@
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>24.415</v>
+        <v>24.332</v>
       </c>
       <c r="AP3" t="n">
-        <v>22.845</v>
+        <v>22.768</v>
       </c>
       <c r="AQ3" t="n">
-        <v>23.258</v>
+        <v>23.179</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
@@ -11443,19 +11473,19 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>47.26</v>
+        <v>47.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>46.103</v>
+        <v>45.947</v>
       </c>
       <c r="AX3" t="n">
-        <v>46.103</v>
+        <v>45.947</v>
       </c>
       <c r="AY3" t="n">
-        <v>70.518</v>
+        <v>70.279</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.46</v>
+        <v>19.04</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -11622,13 +11652,13 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>24.375</v>
+        <v>24.293</v>
       </c>
       <c r="AP4" t="n">
-        <v>23.144</v>
+        <v>23.065</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23.171</v>
+        <v>23.092</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
@@ -11637,19 +11667,19 @@
         <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>47.519</v>
+        <v>47.358</v>
       </c>
       <c r="AW4" t="n">
-        <v>46.315</v>
+        <v>46.157</v>
       </c>
       <c r="AX4" t="n">
-        <v>46.315</v>
+        <v>46.157</v>
       </c>
       <c r="AY4" t="n">
-        <v>70.69</v>
+        <v>70.45</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.49</v>
+        <v>13.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -11820,13 +11850,13 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>24.651</v>
+        <v>24.568</v>
       </c>
       <c r="AP5" t="n">
-        <v>22.49</v>
+        <v>22.414</v>
       </c>
       <c r="AQ5" t="n">
-        <v>23.626</v>
+        <v>23.546</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
@@ -11835,19 +11865,19 @@
         <v>3</v>
       </c>
       <c r="AV5" t="n">
-        <v>47.141</v>
+        <v>46.982</v>
       </c>
       <c r="AW5" t="n">
-        <v>46.116</v>
+        <v>45.96</v>
       </c>
       <c r="AX5" t="n">
-        <v>46.116</v>
+        <v>45.96</v>
       </c>
       <c r="AY5" t="n">
-        <v>70.767</v>
+        <v>70.52800000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.44</v>
+        <v>11.14</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -12018,13 +12048,13 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>23.93</v>
+        <v>23.849</v>
       </c>
       <c r="AP6" t="n">
-        <v>23.089</v>
+        <v>23.011</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23.897</v>
+        <v>23.816</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
@@ -12033,19 +12063,19 @@
         <v>3</v>
       </c>
       <c r="AV6" t="n">
-        <v>47.019</v>
+        <v>46.86</v>
       </c>
       <c r="AW6" t="n">
-        <v>46.986</v>
+        <v>46.827</v>
       </c>
       <c r="AX6" t="n">
-        <v>46.986</v>
+        <v>46.827</v>
       </c>
       <c r="AY6" t="n">
-        <v>70.916</v>
+        <v>70.676</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8.33</v>
+        <v>8.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -12216,13 +12246,13 @@
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>25.348</v>
+        <v>25.263</v>
       </c>
       <c r="AP7" t="n">
-        <v>22.447</v>
+        <v>22.372</v>
       </c>
       <c r="AQ7" t="n">
-        <v>23.174</v>
+        <v>23.096</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
@@ -12231,19 +12261,19 @@
         <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>47.795</v>
+        <v>47.635</v>
       </c>
       <c r="AW7" t="n">
-        <v>45.621</v>
+        <v>45.468</v>
       </c>
       <c r="AX7" t="n">
-        <v>45.621</v>
+        <v>45.468</v>
       </c>
       <c r="AY7" t="n">
-        <v>70.96899999999999</v>
+        <v>70.73099999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.44</v>
+        <v>7.19</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -12297,65 +12327,65 @@
         <v>1200</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13/12/8/8/11/6</t>
+          <t>8/7/11/12/12/11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>瑰麗人生</t>
+          <t>方圓星</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H044</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K517</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>H044</t>
+          <t>K517</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>楊明綸</t>
+          <t>布浩榮</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>丁冠豪</t>
+          <t>羅富全</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="T8" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="U8" t="n">
-        <v>1074</v>
+        <v>1065</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.09.65</t>
+          <t>1.10.21</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
@@ -12365,62 +12395,62 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>23,400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>* 2</t>
+          <t>+ 1</t>
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>B/TT</t>
+          <t>CP/H/TT1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>杜炳坤與陳慎</t>
+          <t>柯詠芝</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>Shamexpress</t>
+          <t>Rebel Dane</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Allawara</t>
+          <t>Braeview Miss</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>24.34</v>
+        <v>24.759</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23.015</v>
+        <v>22.462</v>
       </c>
       <c r="AK8" t="n">
-        <v>23.627</v>
+        <v>23.551</v>
       </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>24.528</v>
+        <v>24.701</v>
       </c>
       <c r="AP8" t="n">
-        <v>22.983</v>
+        <v>22.47</v>
       </c>
       <c r="AQ8" t="n">
-        <v>23.534</v>
+        <v>23.588</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
@@ -12429,23 +12459,23 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>47.511</v>
+        <v>47.171</v>
       </c>
       <c r="AW8" t="n">
-        <v>46.517</v>
+        <v>46.058</v>
       </c>
       <c r="AX8" t="n">
-        <v>46.517</v>
+        <v>46.058</v>
       </c>
       <c r="AY8" t="n">
-        <v>71.045</v>
+        <v>70.759</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.33</v>
+        <v>6.77</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5-6-7</t>
+          <t>7-5-7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -12455,14 +12485,10 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>中置守位 (外檔, 頭段排名6)</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>30%(3/10)</t>
-        </is>
-      </c>
+          <t>中置守位 (中檔, 頭段排名5)</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -12495,65 +12521,65 @@
         <v>1200</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8/7/11/12/12/11</t>
+          <t>13/12/8/8/11/6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>方圓星</t>
+          <t>瑰麗人生</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K517</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H044</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>K517</t>
+          <t>H044</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>潘明輝</t>
+          <t>楊明綸</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>羅富全</t>
+          <t>丁冠豪</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="T9" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="U9" t="n">
-        <v>1065</v>
+        <v>1074</v>
       </c>
       <c r="V9" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.10.21</t>
+          <t>1.09.65</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr">
@@ -12563,62 +12589,62 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23,400</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>+ 1</t>
+          <t>* 2</t>
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>CP/H/TT1</t>
+          <t>B/TT</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>柯詠芝</t>
+          <t>杜炳坤與陳慎</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>Rebel Dane</t>
+          <t>Shamexpress</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Braeview Miss</t>
+          <t>Allawara</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>24.759</v>
+        <v>24.34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>22.462</v>
+        <v>23.015</v>
       </c>
       <c r="AK9" t="n">
-        <v>23.551</v>
+        <v>23.627</v>
       </c>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>24.84</v>
+        <v>24.445</v>
       </c>
       <c r="AP9" t="n">
-        <v>22.596</v>
+        <v>22.905</v>
       </c>
       <c r="AQ9" t="n">
-        <v>23.721</v>
+        <v>23.454</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
@@ -12627,23 +12653,23 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>47.436</v>
+        <v>47.35</v>
       </c>
       <c r="AW9" t="n">
-        <v>46.317</v>
+        <v>46.359</v>
       </c>
       <c r="AX9" t="n">
-        <v>46.317</v>
+        <v>46.359</v>
       </c>
       <c r="AY9" t="n">
-        <v>71.157</v>
+        <v>70.804</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.98</v>
+        <v>6.15</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8-5-8</t>
+          <t>5-6-8</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -12653,12 +12679,12 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>中置守位 (中檔, 頭段排名5)</t>
+          <t>中置守位 (外檔, 頭段排名6)</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>22%(7/32)</t>
+          <t>30%(3/10)</t>
         </is>
       </c>
     </row>
@@ -12810,13 +12836,13 @@
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
-        <v>24.836</v>
+        <v>24.753</v>
       </c>
       <c r="AP10" t="n">
-        <v>22.718</v>
+        <v>22.641</v>
       </c>
       <c r="AQ10" t="n">
-        <v>23.67</v>
+        <v>23.59</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
@@ -12825,23 +12851,23 @@
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>47.554</v>
+        <v>47.394</v>
       </c>
       <c r="AW10" t="n">
-        <v>46.388</v>
+        <v>46.231</v>
       </c>
       <c r="AX10" t="n">
-        <v>46.388</v>
+        <v>46.231</v>
       </c>
       <c r="AY10" t="n">
-        <v>71.224</v>
+        <v>70.98399999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.32</v>
+        <v>4.17</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7-8-9</t>
+          <t>8-8-9</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -13008,13 +13034,13 @@
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
-        <v>24.935</v>
+        <v>24.851</v>
       </c>
       <c r="AP11" t="n">
-        <v>23.28</v>
+        <v>23.202</v>
       </c>
       <c r="AQ11" t="n">
-        <v>23.876</v>
+        <v>23.796</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr"/>
@@ -13023,19 +13049,19 @@
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>48.215</v>
+        <v>48.053</v>
       </c>
       <c r="AW11" t="n">
-        <v>47.156</v>
+        <v>46.998</v>
       </c>
       <c r="AX11" t="n">
-        <v>47.156</v>
+        <v>46.998</v>
       </c>
       <c r="AY11" t="n">
-        <v>72.09099999999999</v>
+        <v>71.849</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -13206,7 +13232,9 @@
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>0.27</v>
+      </c>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -13364,7 +13392,9 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>0.27</v>
+      </c>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -13701,65 +13731,65 @@
         <v>1650</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5/3/9/8/10/11</t>
+          <t>2/4/2/2/8/4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>浪漫老撾</t>
+          <t>隨緣得勝</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2021_G476</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K223</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>G476</t>
+          <t>K223</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>布浩榮</t>
+          <t>周俊樂 (-2)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>巫偉傑</t>
+          <t>游達榮</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>1183</v>
+        <v>1066</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1.38.85</t>
+          <t>1.39.12</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
@@ -13769,7 +13799,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>370,250</t>
+          <t>877,500</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -13778,58 +13808,58 @@
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>CP/TT</t>
+          <t>B/TT</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>鄭強輝</t>
+          <t>正能量團體</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>Pins</t>
+          <t>The Autumn Sun</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Zaburn</t>
+          <t>Prana</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>ISG</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>28.665</v>
+        <v>29.056</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23.655</v>
+        <v>23.855</v>
       </c>
       <c r="AK2" t="n">
-        <v>24.038</v>
+        <v>23.939</v>
       </c>
       <c r="AL2" t="n">
-        <v>24.168</v>
+        <v>23.229</v>
       </c>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>28.343</v>
+        <v>28.976</v>
       </c>
       <c r="AP2" t="n">
-        <v>23.433</v>
+        <v>23.827</v>
       </c>
       <c r="AQ2" t="n">
-        <v>23.955</v>
+        <v>23.974</v>
       </c>
       <c r="AR2" t="n">
-        <v>24.084</v>
+        <v>23.264</v>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
@@ -13837,38 +13867,38 @@
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>51.776</v>
+        <v>52.803</v>
       </c>
       <c r="AW2" t="n">
-        <v>48.039</v>
+        <v>47.238</v>
       </c>
       <c r="AX2" t="n">
-        <v>48.039</v>
+        <v>47.238</v>
       </c>
       <c r="AY2" t="n">
-        <v>99.815</v>
+        <v>100.041</v>
       </c>
       <c r="AZ2" t="n">
-        <v>30.9</v>
+        <v>19.25</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2-2-1-1</t>
+          <t>9-8-8-1</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>前置貼欄</t>
+          <t>留後追趕</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>前置貼欄 (內檔, 頭段排名2)</t>
+          <t>留後追趕 (中檔, 頭段排名8)</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>100%(2/2)</t>
+          <t>33%(5/15)</t>
         </is>
       </c>
     </row>
@@ -13903,65 +13933,65 @@
         <v>1650</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2/4/2/2/8/4</t>
+          <t>5/3/9/8/10/11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>隨緣得勝</t>
+          <t>浪漫老撾</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K223</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2021_G476</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>K223</t>
+          <t>G476</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>周俊樂 (-2)</t>
+          <t>布浩榮</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>游達榮</t>
+          <t>巫偉傑</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1066</v>
+        <v>1183</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.39.12</t>
+          <t>1.38.85</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
@@ -13971,7 +14001,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>877,500</t>
+          <t>370,250</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -13980,58 +14010,58 @@
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>B/TT</t>
+          <t>CP/TT</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>正能量團體</t>
+          <t>鄭強輝</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>The Autumn Sun</t>
+          <t>Pins</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Prana</t>
+          <t>Zaburn</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>ISG</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>29.056</v>
+        <v>28.665</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23.855</v>
+        <v>23.655</v>
       </c>
       <c r="AK3" t="n">
-        <v>23.939</v>
+        <v>24.038</v>
       </c>
       <c r="AL3" t="n">
-        <v>23.229</v>
+        <v>24.168</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>29.075</v>
+        <v>28.417</v>
       </c>
       <c r="AP3" t="n">
-        <v>23.908</v>
+        <v>23.495</v>
       </c>
       <c r="AQ3" t="n">
-        <v>24.056</v>
+        <v>24.018</v>
       </c>
       <c r="AR3" t="n">
-        <v>23.344</v>
+        <v>24.147</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
@@ -14039,38 +14069,38 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>52.983</v>
+        <v>51.912</v>
       </c>
       <c r="AW3" t="n">
-        <v>47.4</v>
+        <v>48.165</v>
       </c>
       <c r="AX3" t="n">
-        <v>47.4</v>
+        <v>48.165</v>
       </c>
       <c r="AY3" t="n">
-        <v>100.383</v>
+        <v>100.077</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16.41</v>
+        <v>18.42</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>9-8-7-2</t>
+          <t>3-3-1-2</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>留後追趕</t>
+          <t>前置貼欄</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>留後追趕 (中檔, 頭段排名8)</t>
+          <t>前置貼欄 (內檔, 頭段排名3)</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>33%(5/15)</t>
+          <t>100%(2/2)</t>
         </is>
       </c>
     </row>
@@ -14224,16 +14254,16 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>28.412</v>
+        <v>28.315</v>
       </c>
       <c r="AP4" t="n">
-        <v>24.099</v>
+        <v>24.017</v>
       </c>
       <c r="AQ4" t="n">
-        <v>24.101</v>
+        <v>24.019</v>
       </c>
       <c r="AR4" t="n">
-        <v>23.918</v>
+        <v>23.837</v>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
@@ -14241,23 +14271,23 @@
         <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>52.511</v>
+        <v>52.332</v>
       </c>
       <c r="AW4" t="n">
-        <v>48.019</v>
+        <v>47.856</v>
       </c>
       <c r="AX4" t="n">
-        <v>48.019</v>
+        <v>47.856</v>
       </c>
       <c r="AY4" t="n">
-        <v>100.53</v>
+        <v>100.188</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.93</v>
+        <v>16.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3-6-4-3</t>
+          <t>2-7-4-3</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -14267,7 +14297,7 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>中置守位 (外檔, 頭段排名6)</t>
+          <t>中置守位 (外檔, 頭段排名7)</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
@@ -14426,16 +14456,16 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>29.018</v>
+        <v>28.919</v>
       </c>
       <c r="AP5" t="n">
-        <v>23.469</v>
+        <v>23.39</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24.187</v>
+        <v>24.105</v>
       </c>
       <c r="AR5" t="n">
-        <v>24.006</v>
+        <v>23.925</v>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
@@ -14443,19 +14473,19 @@
         <v>2</v>
       </c>
       <c r="AV5" t="n">
-        <v>52.487</v>
+        <v>52.309</v>
       </c>
       <c r="AW5" t="n">
-        <v>48.193</v>
+        <v>48.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>48.193</v>
+        <v>48.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>100.68</v>
+        <v>100.339</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.78</v>
+        <v>13.32</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -14628,16 +14658,16 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>28.664</v>
+        <v>28.567</v>
       </c>
       <c r="AP6" t="n">
-        <v>23.392</v>
+        <v>23.313</v>
       </c>
       <c r="AQ6" t="n">
-        <v>24.523</v>
+        <v>24.441</v>
       </c>
       <c r="AR6" t="n">
-        <v>24.276</v>
+        <v>24.194</v>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
@@ -14645,23 +14675,23 @@
         <v>2</v>
       </c>
       <c r="AV6" t="n">
-        <v>52.056</v>
+        <v>51.88</v>
       </c>
       <c r="AW6" t="n">
-        <v>48.799</v>
+        <v>48.635</v>
       </c>
       <c r="AX6" t="n">
-        <v>48.799</v>
+        <v>48.635</v>
       </c>
       <c r="AY6" t="n">
-        <v>100.855</v>
+        <v>100.515</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9.699999999999999</v>
+        <v>10.72</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4-3-3-5</t>
+          <t>4-2-3-5</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -14671,7 +14701,7 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>前置守位 (中檔, 頭段排名3)</t>
+          <t>前置守位 (中檔, 頭段排名2)</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
@@ -14711,65 +14741,65 @@
         <v>1650</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1/8/6/10</t>
+          <t>11/3/9/6/6/3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>上浦福旺</t>
+          <t>大數據</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2025_L102</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H230</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>H230</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>鍾易禮 (-2)</t>
+          <t>田泰安</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>沈集成</t>
+          <t>姚本輝</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="T7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1132</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>1.39.59</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
         <v>6</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1055</v>
-      </c>
-      <c r="V7" t="n">
-        <v>10</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>1.39.43</t>
-        </is>
-      </c>
-      <c r="X7" t="n">
-        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
@@ -14779,7 +14809,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>678,600</t>
+          <t>315,900</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -14792,22 +14822,22 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>CP/TT</t>
+          <t>V</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>金慶源</t>
+          <t>李少隆醫生、鄭立言、鄭立德與陳麒宇</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>Redwood</t>
+          <t>Capitalist</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Ceebeel</t>
+          <t>Solar Burst</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -14816,30 +14846,30 @@
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>28.646</v>
+        <v>28.798</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23.499</v>
+        <v>23.507</v>
       </c>
       <c r="AK7" t="n">
-        <v>24.289</v>
+        <v>24.418</v>
       </c>
       <c r="AL7" t="n">
-        <v>24.083</v>
+        <v>23.94</v>
       </c>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>28.795</v>
+        <v>28.814</v>
       </c>
       <c r="AP7" t="n">
-        <v>23.606</v>
+        <v>23.514</v>
       </c>
       <c r="AQ7" t="n">
-        <v>24.429</v>
+        <v>24.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>24.222</v>
+        <v>23.921</v>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
@@ -14847,23 +14877,23 @@
         <v>3</v>
       </c>
       <c r="AV7" t="n">
-        <v>52.401</v>
+        <v>52.328</v>
       </c>
       <c r="AW7" t="n">
-        <v>48.651</v>
+        <v>48.321</v>
       </c>
       <c r="AX7" t="n">
-        <v>48.651</v>
+        <v>48.321</v>
       </c>
       <c r="AY7" t="n">
-        <v>101.052</v>
+        <v>100.649</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.78</v>
+        <v>9.08</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5-4-6-6</t>
+          <t>7-6-7-6</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -14873,12 +14903,12 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>中置守位 (外檔, 頭段排名4)</t>
+          <t>中置守位 (中檔, 頭段排名6)</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>38%(3/8)</t>
+          <t>30%(3/10)</t>
         </is>
       </c>
     </row>
@@ -14913,65 +14943,65 @@
         <v>1650</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11/3/9/6/6/3</t>
+          <t>1/8/6/10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>大數據</t>
+          <t>上浦福旺</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H230</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2025_L102</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>H230</t>
+          <t>L102</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>潘明輝</t>
+          <t>鍾易禮 (-2)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>姚本輝</t>
+          <t>沈集成</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="T8" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8" t="n">
-        <v>1132</v>
+        <v>1055</v>
       </c>
       <c r="V8" t="n">
-        <v>-6</v>
+        <v>10</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.39.59</t>
+          <t>1.39.43</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
@@ -14981,7 +15011,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>315,900</t>
+          <t>678,600</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -14994,22 +15024,22 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>CP/TT</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>李少隆醫生、鄭立言、鄭立德與陳麒宇</t>
+          <t>金慶源</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>Capitalist</t>
+          <t>Redwood</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Solar Burst</t>
+          <t>Ceebeel</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -15018,30 +15048,30 @@
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>28.798</v>
+        <v>28.646</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23.507</v>
+        <v>23.499</v>
       </c>
       <c r="AK8" t="n">
-        <v>24.418</v>
+        <v>24.289</v>
       </c>
       <c r="AL8" t="n">
-        <v>23.94</v>
+        <v>24.083</v>
       </c>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>28.989</v>
+        <v>28.697</v>
       </c>
       <c r="AP8" t="n">
-        <v>23.657</v>
+        <v>23.526</v>
       </c>
       <c r="AQ8" t="n">
-        <v>24.548</v>
+        <v>24.346</v>
       </c>
       <c r="AR8" t="n">
-        <v>24.066</v>
+        <v>24.14</v>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
@@ -15049,23 +15079,23 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>52.646</v>
+        <v>52.223</v>
       </c>
       <c r="AW8" t="n">
-        <v>48.614</v>
+        <v>48.486</v>
       </c>
       <c r="AX8" t="n">
-        <v>48.614</v>
+        <v>48.486</v>
       </c>
       <c r="AY8" t="n">
-        <v>101.26</v>
+        <v>100.709</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.17</v>
+        <v>8.43</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7-7-8-7</t>
+          <t>5-4-6-7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -15075,12 +15105,12 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>中置守位 (中檔, 頭段排名7)</t>
+          <t>中置守位 (外檔, 頭段排名4)</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>17%(3/18)</t>
+          <t>38%(3/8)</t>
         </is>
       </c>
     </row>
@@ -15234,16 +15264,16 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>27.946</v>
+        <v>27.852</v>
       </c>
       <c r="AP9" t="n">
-        <v>23.437</v>
+        <v>23.358</v>
       </c>
       <c r="AQ9" t="n">
-        <v>25.062</v>
+        <v>24.978</v>
       </c>
       <c r="AR9" t="n">
-        <v>25.846</v>
+        <v>25.759</v>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
@@ -15251,19 +15281,19 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>51.383</v>
+        <v>51.21</v>
       </c>
       <c r="AW9" t="n">
-        <v>50.908</v>
+        <v>50.737</v>
       </c>
       <c r="AX9" t="n">
-        <v>50.908</v>
+        <v>50.737</v>
       </c>
       <c r="AY9" t="n">
-        <v>102.291</v>
+        <v>101.947</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -15436,16 +15466,16 @@
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
-        <v>28.802</v>
+        <v>28.705</v>
       </c>
       <c r="AP10" t="n">
-        <v>24.532</v>
+        <v>24.449</v>
       </c>
       <c r="AQ10" t="n">
-        <v>25.331</v>
+        <v>25.246</v>
       </c>
       <c r="AR10" t="n">
-        <v>23.947</v>
+        <v>23.866</v>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
@@ -15453,19 +15483,19 @@
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>53.334</v>
+        <v>53.154</v>
       </c>
       <c r="AW10" t="n">
-        <v>49.278</v>
+        <v>49.112</v>
       </c>
       <c r="AX10" t="n">
-        <v>49.278</v>
+        <v>49.112</v>
       </c>
       <c r="AY10" t="n">
-        <v>102.612</v>
+        <v>102.266</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -15636,7 +15666,9 @@
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>0.55</v>
+      </c>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -15794,7 +15826,9 @@
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>0.55</v>
+      </c>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -15952,7 +15986,9 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>0.55</v>
+      </c>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -16408,13 +16444,13 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>12.518</v>
+        <v>12.475</v>
       </c>
       <c r="AP2" t="n">
-        <v>20.79</v>
+        <v>20.72</v>
       </c>
       <c r="AQ2" t="n">
-        <v>22.591</v>
+        <v>22.514</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
@@ -16423,19 +16459,19 @@
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>33.308</v>
+        <v>33.195</v>
       </c>
       <c r="AW2" t="n">
-        <v>43.381</v>
+        <v>43.234</v>
       </c>
       <c r="AX2" t="n">
-        <v>43.381</v>
+        <v>43.234</v>
       </c>
       <c r="AY2" t="n">
-        <v>55.899</v>
+        <v>55.709</v>
       </c>
       <c r="AZ2" t="n">
-        <v>55.17</v>
+        <v>53.87</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -16606,13 +16642,13 @@
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>12.551</v>
+        <v>12.509</v>
       </c>
       <c r="AP3" t="n">
-        <v>20.859</v>
+        <v>20.788</v>
       </c>
       <c r="AQ3" t="n">
-        <v>23.169</v>
+        <v>23.091</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
@@ -16621,19 +16657,19 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>33.41</v>
+        <v>33.297</v>
       </c>
       <c r="AW3" t="n">
-        <v>44.028</v>
+        <v>43.879</v>
       </c>
       <c r="AX3" t="n">
-        <v>44.028</v>
+        <v>43.879</v>
       </c>
       <c r="AY3" t="n">
-        <v>56.579</v>
+        <v>56.388</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.68</v>
+        <v>12.35</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -16804,13 +16840,13 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>12.539</v>
+        <v>12.496</v>
       </c>
       <c r="AP4" t="n">
-        <v>20.977</v>
+        <v>20.906</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23.206</v>
+        <v>23.127</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
@@ -16819,19 +16855,19 @@
         <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>33.516</v>
+        <v>33.402</v>
       </c>
       <c r="AW4" t="n">
-        <v>44.183</v>
+        <v>44.033</v>
       </c>
       <c r="AX4" t="n">
-        <v>44.183</v>
+        <v>44.033</v>
       </c>
       <c r="AY4" t="n">
-        <v>56.722</v>
+        <v>56.529</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9.31</v>
+        <v>9.09</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -17002,13 +17038,13 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>13.152</v>
+        <v>13.108</v>
       </c>
       <c r="AP5" t="n">
-        <v>21.82</v>
+        <v>21.746</v>
       </c>
       <c r="AQ5" t="n">
-        <v>21.824</v>
+        <v>21.75</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
@@ -17017,19 +17053,19 @@
         <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>34.972</v>
+        <v>34.854</v>
       </c>
       <c r="AW5" t="n">
-        <v>43.644</v>
+        <v>43.496</v>
       </c>
       <c r="AX5" t="n">
-        <v>43.644</v>
+        <v>43.496</v>
       </c>
       <c r="AY5" t="n">
-        <v>56.796</v>
+        <v>56.604</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.93</v>
+        <v>7.73</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -17200,13 +17236,13 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>12.896</v>
+        <v>12.852</v>
       </c>
       <c r="AP6" t="n">
-        <v>21.567</v>
+        <v>21.494</v>
       </c>
       <c r="AQ6" t="n">
-        <v>22.375</v>
+        <v>22.299</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
@@ -17215,19 +17251,19 @@
         <v>3</v>
       </c>
       <c r="AV6" t="n">
-        <v>34.463</v>
+        <v>34.346</v>
       </c>
       <c r="AW6" t="n">
-        <v>43.942</v>
+        <v>43.793</v>
       </c>
       <c r="AX6" t="n">
-        <v>43.942</v>
+        <v>43.793</v>
       </c>
       <c r="AY6" t="n">
-        <v>56.838</v>
+        <v>56.645</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7.24</v>
+        <v>7.07</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -17400,13 +17436,13 @@
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>12.808</v>
+        <v>12.764</v>
       </c>
       <c r="AP7" t="n">
-        <v>21.289</v>
+        <v>21.217</v>
       </c>
       <c r="AQ7" t="n">
-        <v>22.851</v>
+        <v>22.774</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
@@ -17415,19 +17451,19 @@
         <v>2</v>
       </c>
       <c r="AV7" t="n">
-        <v>34.097</v>
+        <v>33.981</v>
       </c>
       <c r="AW7" t="n">
-        <v>44.14</v>
+        <v>43.991</v>
       </c>
       <c r="AX7" t="n">
-        <v>44.14</v>
+        <v>43.991</v>
       </c>
       <c r="AY7" t="n">
-        <v>56.948</v>
+        <v>56.755</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.71</v>
+        <v>5.57</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -17598,13 +17634,13 @@
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>12.772</v>
+        <v>12.729</v>
       </c>
       <c r="AP8" t="n">
-        <v>21.419</v>
+        <v>21.346</v>
       </c>
       <c r="AQ8" t="n">
-        <v>23.252</v>
+        <v>23.173</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
@@ -17613,19 +17649,19 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>34.191</v>
+        <v>34.075</v>
       </c>
       <c r="AW8" t="n">
-        <v>44.671</v>
+        <v>44.519</v>
       </c>
       <c r="AX8" t="n">
-        <v>44.671</v>
+        <v>44.519</v>
       </c>
       <c r="AY8" t="n">
-        <v>57.443</v>
+        <v>57.248</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -17800,7 +17836,9 @@
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>0.8</v>
+      </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
@@ -17960,7 +17998,9 @@
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>0.8</v>
+      </c>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr"/>
@@ -18118,7 +18158,9 @@
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>0.8</v>
+      </c>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -18572,13 +18614,13 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>23.602</v>
+        <v>23.522</v>
       </c>
       <c r="AP2" t="n">
-        <v>22.721</v>
+        <v>22.644</v>
       </c>
       <c r="AQ2" t="n">
-        <v>23.011</v>
+        <v>22.933</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
@@ -18587,19 +18629,19 @@
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>46.323</v>
+        <v>46.166</v>
       </c>
       <c r="AW2" t="n">
-        <v>45.732</v>
+        <v>45.577</v>
       </c>
       <c r="AX2" t="n">
-        <v>45.732</v>
+        <v>45.577</v>
       </c>
       <c r="AY2" t="n">
-        <v>69.334</v>
+        <v>69.099</v>
       </c>
       <c r="AZ2" t="n">
-        <v>25.28</v>
+        <v>24.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -18766,13 +18808,13 @@
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>24.392</v>
+        <v>24.309</v>
       </c>
       <c r="AP3" t="n">
-        <v>22.56</v>
+        <v>22.483</v>
       </c>
       <c r="AQ3" t="n">
-        <v>22.471</v>
+        <v>22.394</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
@@ -18781,19 +18823,19 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>46.952</v>
+        <v>46.792</v>
       </c>
       <c r="AW3" t="n">
-        <v>45.031</v>
+        <v>44.877</v>
       </c>
       <c r="AX3" t="n">
-        <v>45.031</v>
+        <v>44.877</v>
       </c>
       <c r="AY3" t="n">
-        <v>69.423</v>
+        <v>69.18600000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22.51</v>
+        <v>21.91</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -18966,13 +19008,13 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>23.981</v>
+        <v>23.899</v>
       </c>
       <c r="AP4" t="n">
-        <v>22.749</v>
+        <v>22.672</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22.898</v>
+        <v>22.82</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
@@ -18981,19 +19023,19 @@
         <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>46.73</v>
+        <v>46.571</v>
       </c>
       <c r="AW4" t="n">
-        <v>45.647</v>
+        <v>45.492</v>
       </c>
       <c r="AX4" t="n">
-        <v>45.647</v>
+        <v>45.492</v>
       </c>
       <c r="AY4" t="n">
-        <v>69.628</v>
+        <v>69.39100000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17.23</v>
+        <v>16.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -19166,13 +19208,13 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>24.135</v>
+        <v>24.053</v>
       </c>
       <c r="AP5" t="n">
-        <v>22.562</v>
+        <v>22.486</v>
       </c>
       <c r="AQ5" t="n">
-        <v>23.05</v>
+        <v>22.971</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
@@ -19181,19 +19223,19 @@
         <v>3</v>
       </c>
       <c r="AV5" t="n">
-        <v>46.697</v>
+        <v>46.539</v>
       </c>
       <c r="AW5" t="n">
-        <v>45.612</v>
+        <v>45.457</v>
       </c>
       <c r="AX5" t="n">
-        <v>45.612</v>
+        <v>45.457</v>
       </c>
       <c r="AY5" t="n">
-        <v>69.747</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.76</v>
+        <v>14.35</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -19364,13 +19406,13 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>24.251</v>
+        <v>24.168</v>
       </c>
       <c r="AP6" t="n">
-        <v>22.577</v>
+        <v>22.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23.196</v>
+        <v>23.117</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
@@ -19379,19 +19421,19 @@
         <v>3</v>
       </c>
       <c r="AV6" t="n">
-        <v>46.828</v>
+        <v>46.668</v>
       </c>
       <c r="AW6" t="n">
-        <v>45.773</v>
+        <v>45.617</v>
       </c>
       <c r="AX6" t="n">
-        <v>45.773</v>
+        <v>45.617</v>
       </c>
       <c r="AY6" t="n">
-        <v>70.024</v>
+        <v>69.785</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10.29</v>
+        <v>10.02</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -19562,13 +19604,13 @@
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>25.005</v>
+        <v>24.92</v>
       </c>
       <c r="AP7" t="n">
-        <v>22.485</v>
+        <v>22.409</v>
       </c>
       <c r="AQ7" t="n">
-        <v>23.059</v>
+        <v>22.982</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
@@ -19577,19 +19619,19 @@
         <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>47.49</v>
+        <v>47.329</v>
       </c>
       <c r="AW7" t="n">
-        <v>45.544</v>
+        <v>45.391</v>
       </c>
       <c r="AX7" t="n">
-        <v>45.544</v>
+        <v>45.391</v>
       </c>
       <c r="AY7" t="n">
-        <v>70.54900000000001</v>
+        <v>70.31100000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.19</v>
+        <v>5.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -19756,13 +19798,13 @@
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>24.559</v>
+        <v>24.476</v>
       </c>
       <c r="AP8" t="n">
-        <v>22.635</v>
+        <v>22.558</v>
       </c>
       <c r="AQ8" t="n">
-        <v>23.74</v>
+        <v>23.66</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
@@ -19771,19 +19813,19 @@
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>47.194</v>
+        <v>47.034</v>
       </c>
       <c r="AW8" t="n">
-        <v>46.375</v>
+        <v>46.218</v>
       </c>
       <c r="AX8" t="n">
-        <v>46.375</v>
+        <v>46.218</v>
       </c>
       <c r="AY8" t="n">
-        <v>70.934</v>
+        <v>70.694</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -19954,13 +19996,13 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>24.017</v>
+        <v>23.936</v>
       </c>
       <c r="AP9" t="n">
-        <v>22.538</v>
+        <v>22.462</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24.9</v>
+        <v>24.816</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
@@ -19969,19 +20011,19 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>46.555</v>
+        <v>46.398</v>
       </c>
       <c r="AW9" t="n">
-        <v>47.438</v>
+        <v>47.278</v>
       </c>
       <c r="AX9" t="n">
-        <v>47.438</v>
+        <v>47.278</v>
       </c>
       <c r="AY9" t="n">
-        <v>71.455</v>
+        <v>71.214</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -20062,7 +20104,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>潘明輝</t>
+          <t>梁家俊</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -20152,13 +20194,15 @@
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>0.7</v>
+      </c>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>22%(7/32)</t>
+          <t>34%(10/29)</t>
         </is>
       </c>
     </row>
@@ -20310,7 +20354,9 @@
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>0.7</v>
+      </c>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
@@ -20468,7 +20514,9 @@
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>0.7</v>
+      </c>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
@@ -20626,7 +20674,9 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>0.7</v>
+      </c>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
@@ -21082,16 +21132,16 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>27.924</v>
+        <v>27.829</v>
       </c>
       <c r="AP2" t="n">
-        <v>23.859</v>
+        <v>23.778</v>
       </c>
       <c r="AQ2" t="n">
-        <v>23.8</v>
+        <v>23.719</v>
       </c>
       <c r="AR2" t="n">
-        <v>23.392</v>
+        <v>23.312</v>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
@@ -21099,19 +21149,19 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>51.783</v>
+        <v>51.607</v>
       </c>
       <c r="AW2" t="n">
-        <v>47.192</v>
+        <v>47.031</v>
       </c>
       <c r="AX2" t="n">
-        <v>47.192</v>
+        <v>47.031</v>
       </c>
       <c r="AY2" t="n">
-        <v>98.97499999999999</v>
+        <v>98.63800000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>34.73</v>
+        <v>38.69</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -21165,65 +21215,65 @@
         <v>1650</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1/2/5/5/8/7</t>
+          <t>8/9/9/2/4/12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>凡凡有餘</t>
+          <t>爆笑</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2023_J364</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2023_J079</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>J364</t>
+          <t>J079</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>布浩榮</t>
+          <t>黃寶妮 (-7)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>沈集成</t>
+          <t>告東尼</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1096</v>
+      </c>
+      <c r="V3" t="n">
+        <v>14</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1.38.55</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
         <v>6</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1210</v>
-      </c>
-      <c r="V3" t="n">
-        <v>3</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.38.85</t>
-        </is>
-      </c>
-      <c r="X3" t="n">
-        <v>5</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
@@ -21233,35 +21283,35 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2,449,950</t>
+          <t>2,356,700</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>XB/TT</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>范思浩先生及夫人、范展昕與范展敏</t>
+          <t>何猷亨</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>Justify</t>
+          <t>Deep Field</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Tails Wins</t>
+          <t>Divine City</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -21270,30 +21320,30 @@
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>28.533</v>
+        <v>28.64</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23.948</v>
+        <v>23.884</v>
       </c>
       <c r="AK3" t="n">
-        <v>23.647</v>
+        <v>23.947</v>
       </c>
       <c r="AL3" t="n">
-        <v>23.299</v>
+        <v>23.761</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>28.569</v>
+        <v>28.284</v>
       </c>
       <c r="AP3" t="n">
-        <v>23.95</v>
+        <v>23.652</v>
       </c>
       <c r="AQ3" t="n">
-        <v>23.577</v>
+        <v>23.777</v>
       </c>
       <c r="AR3" t="n">
-        <v>23.229</v>
+        <v>23.592</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
@@ -21301,36 +21351,40 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>52.519</v>
+        <v>51.936</v>
       </c>
       <c r="AW3" t="n">
-        <v>46.806</v>
+        <v>47.369</v>
       </c>
       <c r="AX3" t="n">
-        <v>46.806</v>
+        <v>47.369</v>
       </c>
       <c r="AY3" t="n">
-        <v>99.325</v>
+        <v>99.30500000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22.13</v>
+        <v>15.59</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>6-5-3-2</t>
+          <t>4-4-2-2</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>中置守位</t>
+          <t>前置貼欄</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>中置守位 (中檔, 頭段排名5)</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr"/>
+          <t>前置貼欄 (內檔, 頭段排名4)</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>67%(2/3)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -21363,65 +21417,65 @@
         <v>1650</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8/9/9/2/4/12</t>
+          <t>1/2/5/5/8/7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>爆笑</t>
+          <t>凡凡有餘</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2023_J079</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2023_J364</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>J079</t>
+          <t>J364</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>黃寶妮 (-7)</t>
+          <t>布浩榮</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>告東尼</t>
+          <t>沈集成</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T4" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
       <c r="U4" t="n">
-        <v>1096</v>
+        <v>1210</v>
       </c>
       <c r="V4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.38.55</t>
+          <t>1.38.85</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
@@ -21431,35 +21485,35 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2,356,700</t>
+          <t>2,449,950</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>XB/TT</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>何猷亨</t>
+          <t>范思浩先生及夫人、范展昕與范展敏</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Deep Field</t>
+          <t>Justify</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Divine City</t>
+          <t>Tails Wins</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -21468,30 +21522,30 @@
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>28.64</v>
+        <v>28.533</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23.884</v>
+        <v>23.948</v>
       </c>
       <c r="AK4" t="n">
-        <v>23.947</v>
+        <v>23.647</v>
       </c>
       <c r="AL4" t="n">
-        <v>23.761</v>
+        <v>23.299</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>28.381</v>
+        <v>28.569</v>
       </c>
       <c r="AP4" t="n">
-        <v>23.733</v>
+        <v>23.95</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23.858</v>
+        <v>23.577</v>
       </c>
       <c r="AR4" t="n">
-        <v>23.673</v>
+        <v>23.229</v>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
@@ -21499,40 +21553,36 @@
         <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>52.114</v>
+        <v>52.519</v>
       </c>
       <c r="AW4" t="n">
-        <v>47.531</v>
+        <v>46.806</v>
       </c>
       <c r="AX4" t="n">
-        <v>47.531</v>
+        <v>46.806</v>
       </c>
       <c r="AY4" t="n">
-        <v>99.645</v>
+        <v>99.325</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.66</v>
+        <v>15.17</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4-4-2-3</t>
+          <t>6-6-4-3</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>前置貼欄</t>
+          <t>中置守位</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>前置貼欄 (內檔, 頭段排名4)</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>67%(2/3)</t>
-        </is>
-      </c>
+          <t>中置守位 (中檔, 頭段排名6)</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -21565,65 +21615,65 @@
         <v>1650</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7/6/8/8/1/8</t>
+          <t>4/2/3/4/5/9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>雙星報喜</t>
+          <t>瑪瑙</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K126</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2021_G306</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>K126</t>
+          <t>G306</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>班德禮</t>
+          <t>梁家俊</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>呂健威</t>
+          <t>羅富全</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1155</v>
+      </c>
+      <c r="V5" t="n">
         <v>-2</v>
       </c>
-      <c r="U5" t="n">
-        <v>1249</v>
-      </c>
-      <c r="V5" t="n">
-        <v>13</v>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.39.83</t>
+          <t>1.39.02</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
@@ -21633,7 +21683,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>696,200</t>
+          <t>1,171,200</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -21642,26 +21692,26 @@
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>CP</t>
+          <t>V-/B2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>文壽強與黃豪</t>
+          <t>Chong Min Onn</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>D'Argento</t>
+          <t>All Too Hard</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>You're Dreamin</t>
+          <t>Urban Rocker</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -21670,69 +21720,69 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>28.85</v>
+        <v>28.737</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24.18</v>
+        <v>23.84</v>
       </c>
       <c r="AK5" t="n">
-        <v>23.34</v>
+        <v>23.953</v>
       </c>
       <c r="AL5" t="n">
-        <v>23.46</v>
+        <v>23.33</v>
       </c>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>28.999</v>
+        <v>28.81</v>
       </c>
       <c r="AP5" t="n">
-        <v>24.306</v>
+        <v>23.869</v>
       </c>
       <c r="AQ5" t="n">
-        <v>23.471</v>
+        <v>23.951</v>
       </c>
       <c r="AR5" t="n">
-        <v>23.591</v>
+        <v>23.328</v>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV5" t="n">
-        <v>53.305</v>
+        <v>52.679</v>
       </c>
       <c r="AW5" t="n">
-        <v>47.062</v>
+        <v>47.279</v>
       </c>
       <c r="AX5" t="n">
-        <v>47.062</v>
+        <v>47.279</v>
       </c>
       <c r="AY5" t="n">
-        <v>100.367</v>
+        <v>99.958</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.78</v>
+        <v>6.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>10-10-7-4</t>
+          <t>7-8-8-4</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>留後追趕</t>
+          <t>中置守位</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>留後追趕 (中檔, 頭段排名10)</t>
+          <t>中置守位 (外檔, 頭段排名8)</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>25%(1/4)</t>
+          <t>34%(10/29)</t>
         </is>
       </c>
     </row>
@@ -21767,65 +21817,65 @@
         <v>1650</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4/6/1/1/1/8</t>
+          <t>7/6/8/8/1/8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>翠兒威威</t>
+          <t>雙星報喜</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K084</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K126</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>K084</t>
+          <t>K126</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>周俊樂 (-2)</t>
+          <t>班德禮</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>巫偉傑</t>
+          <t>呂健威</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="U6" t="n">
-        <v>1153</v>
+        <v>1249</v>
       </c>
       <c r="V6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.38.82</t>
+          <t>1.39.83</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
@@ -21835,7 +21885,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2,375,300</t>
+          <t>696,200</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -21848,22 +21898,22 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>CP/TT</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>陳橋森</t>
+          <t>文壽強與黃豪</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>Cappella Sansevero</t>
+          <t>D'Argento</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Passified Lady</t>
+          <t>You're Dreamin</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -21872,69 +21922,69 @@
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>28.185</v>
+        <v>28.85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23.871</v>
+        <v>24.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>23.767</v>
+        <v>23.34</v>
       </c>
       <c r="AL6" t="n">
-        <v>23.905</v>
+        <v>23.46</v>
       </c>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>28.528</v>
+        <v>28.901</v>
       </c>
       <c r="AP6" t="n">
-        <v>24.084</v>
+        <v>24.224</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23.886</v>
+        <v>23.391</v>
       </c>
       <c r="AR6" t="n">
-        <v>24.025</v>
+        <v>23.512</v>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>52.612</v>
+        <v>53.125</v>
       </c>
       <c r="AW6" t="n">
-        <v>47.911</v>
+        <v>46.903</v>
       </c>
       <c r="AX6" t="n">
-        <v>47.911</v>
+        <v>46.903</v>
       </c>
       <c r="AY6" t="n">
-        <v>100.523</v>
+        <v>100.028</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.73</v>
+        <v>5.82</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5-6-5-5</t>
+          <t>10-10-7-5</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>中置守位</t>
+          <t>留後追趕</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>中置守位 (外檔, 頭段排名6)</t>
+          <t>留後追趕 (中檔, 頭段排名10)</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>20%(6/30)</t>
+          <t>25%(1/4)</t>
         </is>
       </c>
     </row>
@@ -21969,65 +22019,65 @@
         <v>1650</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4/2/3/4/5/9</t>
+          <t>4/6/1/1/1/8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>瑪瑙</t>
+          <t>翠兒威威</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2021_G306</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K084</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>G306</t>
+          <t>K084</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>潘明輝</t>
+          <t>周俊樂 (-2)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>羅富全</t>
+          <t>巫偉傑</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="V7" t="n">
-        <v>-2</v>
+        <v>12</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.39.02</t>
+          <t>1.38.82</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
@@ -22037,7 +22087,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1,171,200</t>
+          <t>2,375,300</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -22046,26 +22096,26 @@
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>V-/B2</t>
+          <t>CP/TT</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Chong Min Onn</t>
+          <t>陳橋森</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>All Too Hard</t>
+          <t>Cappella Sansevero</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Urban Rocker</t>
+          <t>Passified Lady</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -22074,30 +22124,30 @@
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>28.737</v>
+        <v>28.185</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23.84</v>
+        <v>23.871</v>
       </c>
       <c r="AK7" t="n">
-        <v>23.953</v>
+        <v>23.767</v>
       </c>
       <c r="AL7" t="n">
-        <v>23.33</v>
+        <v>23.905</v>
       </c>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>28.981</v>
+        <v>28.432</v>
       </c>
       <c r="AP7" t="n">
-        <v>24.01</v>
+        <v>24.002</v>
       </c>
       <c r="AQ7" t="n">
-        <v>24.093</v>
+        <v>23.806</v>
       </c>
       <c r="AR7" t="n">
-        <v>23.466</v>
+        <v>23.944</v>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
@@ -22105,23 +22155,23 @@
         <v>3</v>
       </c>
       <c r="AV7" t="n">
-        <v>52.991</v>
+        <v>52.434</v>
       </c>
       <c r="AW7" t="n">
-        <v>47.559</v>
+        <v>47.75</v>
       </c>
       <c r="AX7" t="n">
-        <v>47.559</v>
+        <v>47.75</v>
       </c>
       <c r="AY7" t="n">
-        <v>100.55</v>
+        <v>100.184</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.57</v>
+        <v>4.71</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>9-8-9-6</t>
+          <t>5-5-5-6</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -22131,12 +22181,12 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>中置守位 (外檔, 頭段排名8)</t>
+          <t>中置守位 (外檔, 頭段排名5)</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>22%(7/32)</t>
+          <t>20%(6/30)</t>
         </is>
       </c>
     </row>
@@ -22286,16 +22336,16 @@
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>28.948</v>
+        <v>28.85</v>
       </c>
       <c r="AP8" t="n">
-        <v>23.818</v>
+        <v>23.737</v>
       </c>
       <c r="AQ8" t="n">
-        <v>24.238</v>
+        <v>24.156</v>
       </c>
       <c r="AR8" t="n">
-        <v>23.687</v>
+        <v>23.607</v>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
@@ -22303,23 +22353,23 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>52.766</v>
+        <v>52.587</v>
       </c>
       <c r="AW8" t="n">
-        <v>47.925</v>
+        <v>47.763</v>
       </c>
       <c r="AX8" t="n">
-        <v>47.925</v>
+        <v>47.763</v>
       </c>
       <c r="AY8" t="n">
-        <v>100.691</v>
+        <v>100.35</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8-7-8-7</t>
+          <t>9-7-9-7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -22488,16 +22538,16 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>27.822</v>
+        <v>27.729</v>
       </c>
       <c r="AP9" t="n">
-        <v>23.816</v>
+        <v>23.736</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24.489</v>
+        <v>24.407</v>
       </c>
       <c r="AR9" t="n">
-        <v>24.588</v>
+        <v>24.506</v>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
@@ -22505,23 +22555,23 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>51.638</v>
+        <v>51.465</v>
       </c>
       <c r="AW9" t="n">
-        <v>49.077</v>
+        <v>48.913</v>
       </c>
       <c r="AX9" t="n">
-        <v>49.077</v>
+        <v>48.913</v>
       </c>
       <c r="AY9" t="n">
-        <v>100.715</v>
+        <v>100.378</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1-1-4-8</t>
+          <t>1-1-3-8</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -22690,16 +22740,16 @@
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
-        <v>28.217</v>
+        <v>28.122</v>
       </c>
       <c r="AP10" t="n">
-        <v>23.706</v>
+        <v>23.625</v>
       </c>
       <c r="AQ10" t="n">
-        <v>24.675</v>
+        <v>24.591</v>
       </c>
       <c r="AR10" t="n">
-        <v>24.46</v>
+        <v>24.377</v>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
@@ -22707,19 +22757,19 @@
         <v>3</v>
       </c>
       <c r="AV10" t="n">
-        <v>51.923</v>
+        <v>51.747</v>
       </c>
       <c r="AW10" t="n">
-        <v>49.135</v>
+        <v>48.968</v>
       </c>
       <c r="AX10" t="n">
-        <v>49.135</v>
+        <v>48.968</v>
       </c>
       <c r="AY10" t="n">
-        <v>101.058</v>
+        <v>100.715</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -22892,16 +22942,16 @@
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
-        <v>28.92</v>
+        <v>28.823</v>
       </c>
       <c r="AP11" t="n">
-        <v>24.071</v>
+        <v>23.99</v>
       </c>
       <c r="AQ11" t="n">
-        <v>24.345</v>
+        <v>24.263</v>
       </c>
       <c r="AR11" t="n">
-        <v>23.883</v>
+        <v>23.803</v>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
@@ -22909,33 +22959,33 @@
         <v>3</v>
       </c>
       <c r="AV11" t="n">
-        <v>52.991</v>
+        <v>52.813</v>
       </c>
       <c r="AW11" t="n">
-        <v>48.228</v>
+        <v>48.066</v>
       </c>
       <c r="AX11" t="n">
-        <v>48.228</v>
+        <v>48.066</v>
       </c>
       <c r="AY11" t="n">
-        <v>101.219</v>
+        <v>100.879</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7-8-10-10</t>
+          <t>8-9-10-10</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>包廂跟前</t>
+          <t>留後追趕</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>包廂跟前 (內檔, 頭段排名8)</t>
+          <t>留後追趕 (內檔, 頭段排名9)</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
@@ -23094,16 +23144,16 @@
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
-        <v>29.809</v>
+        <v>29.708</v>
       </c>
       <c r="AP12" t="n">
-        <v>24.257</v>
+        <v>24.175</v>
       </c>
       <c r="AQ12" t="n">
-        <v>24.12</v>
+        <v>24.038</v>
       </c>
       <c r="AR12" t="n">
-        <v>23.188</v>
+        <v>23.11</v>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
@@ -23111,19 +23161,19 @@
         <v>3</v>
       </c>
       <c r="AV12" t="n">
-        <v>54.066</v>
+        <v>53.883</v>
       </c>
       <c r="AW12" t="n">
-        <v>47.308</v>
+        <v>47.148</v>
       </c>
       <c r="AX12" t="n">
-        <v>47.308</v>
+        <v>47.148</v>
       </c>
       <c r="AY12" t="n">
-        <v>101.374</v>
+        <v>101.031</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -23290,7 +23340,9 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>0.67</v>
+      </c>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
